--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -53,18 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>В5782КН</t>
@@ -134,8 +122,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -221,11 +210,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -233,9 +223,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,20 +579,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>45</v>
@@ -620,7 +610,7 @@
         <v>68.84999999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -630,20 +620,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46150</v>
       </c>
       <c r="B3">
         <v>1158</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>37.627</v>
@@ -661,7 +651,7 @@
         <v>31.23</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -671,20 +661,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46154</v>
       </c>
       <c r="B4">
         <v>1911</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>30.195</v>
@@ -702,7 +692,7 @@
         <v>24.76</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -712,20 +702,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
+      <c r="A5" s="2">
+        <v>46157</v>
       </c>
       <c r="B5">
         <v>1158</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>41</v>
@@ -743,7 +733,7 @@
         <v>63.14</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -753,103 +743,103 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6">
+        <v>86</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.5048</v>
+      </c>
+      <c r="E10" s="6">
+        <v>129.41</v>
+      </c>
+      <c r="F10" s="6">
+        <v>131.99</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="6">
+        <v>67.822</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.8155</v>
+      </c>
+      <c r="E11" s="6">
+        <v>55.31</v>
+      </c>
+      <c r="F11" s="6">
+        <v>55.99</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5">
-        <v>86</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1.5048</v>
-      </c>
-      <c r="E10" s="5">
-        <v>129.41</v>
-      </c>
-      <c r="F10" s="5">
-        <v>131.99</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5">
-        <v>67.822</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.8155</v>
-      </c>
-      <c r="E11" s="5">
-        <v>55.31</v>
-      </c>
-      <c r="F11" s="5">
-        <v>55.99</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>153.822</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>184.72</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>187.98</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>3.26</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -167,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,12 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,17 +227,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,19 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>В5782КН</t>
@@ -70,7 +61,7 @@
     <t>В7241ВР</t>
   </si>
   <si>
-    <t>В6514КС</t>
+    <t>В8981ВР</t>
   </si>
   <si>
     <t>78970155027721376</t>
@@ -79,40 +70,13 @@
     <t>78970155027721400</t>
   </si>
   <si>
-    <t>78970155027721384</t>
+    <t>78970155027721392</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:19:00</t>
-  </si>
-  <si>
-    <t>14:33:00</t>
-  </si>
-  <si>
-    <t>14:29:00</t>
-  </si>
-  <si>
-    <t>16:19:00</t>
-  </si>
-  <si>
-    <t>3232409633 3232409633</t>
-  </si>
-  <si>
-    <t>3232521559 3232521559</t>
-  </si>
-  <si>
-    <t>3232528295 3232528295</t>
-  </si>
-  <si>
-    <t>3232531914 3232531914</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -532,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +505,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,283 +546,273 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>61.6</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>62.8</v>
+      </c>
+      <c r="K2">
+        <v>279360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>65.52</v>
+      </c>
+      <c r="K3">
+        <v>279530</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H4">
+        <v>21.76</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J4">
+        <v>22.08</v>
+      </c>
+      <c r="K4">
+        <v>55289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>29.97</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H5">
+        <v>20.38</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J5">
+        <v>20.68</v>
+      </c>
+      <c r="K5">
+        <v>81560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H6">
+        <v>59.67</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J6">
+        <v>60.84</v>
+      </c>
+      <c r="K6">
+        <v>279830</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>47</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H2">
-        <v>1.54</v>
-      </c>
-      <c r="I2" s="1">
-        <v>72.38</v>
-      </c>
-      <c r="J2">
-        <v>1.57</v>
-      </c>
-      <c r="K2" s="1">
-        <v>73.79000000000001</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="D10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2">
-        <v>278985</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7">
+        <v>121</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.5333</v>
+      </c>
+      <c r="E11" s="7">
+        <v>185.53</v>
+      </c>
+      <c r="F11" s="7">
+        <v>189.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15.4</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.7</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="B12" s="7">
+        <v>61.97</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="E12" s="7">
+        <v>42.14</v>
+      </c>
+      <c r="F12" s="7">
+        <v>42.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>37.69</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>0.76</v>
-      </c>
-      <c r="I4" s="1">
-        <v>28.64</v>
-      </c>
-      <c r="J4">
-        <v>0.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>29.02</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>54920</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>75.45999999999999</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>76.93000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>260764</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="7">
-        <v>106</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.54</v>
-      </c>
-      <c r="E10" s="7">
-        <v>163.24</v>
-      </c>
-      <c r="F10" s="7">
-        <v>166.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="7">
-        <v>37.69</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.7599</v>
-      </c>
-      <c r="E11" s="7">
-        <v>28.64</v>
-      </c>
-      <c r="F11" s="7">
-        <v>29.02</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10">
-        <v>143.69</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>191.88</v>
-      </c>
-      <c r="F12" s="10">
-        <v>195.44</v>
+      <c r="B13" s="10">
+        <v>182.97</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>227.67</v>
+      </c>
+      <c r="F13" s="10">
+        <v>231.92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В5782КН</t>
@@ -77,6 +83,21 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>16:14</t>
+  </si>
+  <si>
+    <t>12:13</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -496,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,10 +530,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,22 +569,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46177</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>40</v>
@@ -578,25 +607,31 @@
       <c r="J2">
         <v>62.8</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
         <v>279360</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>107346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46181</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -613,25 +648,31 @@
       <c r="J3">
         <v>65.52</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
         <v>279530</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>109665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46184</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>32</v>
@@ -648,25 +689,31 @@
       <c r="J4">
         <v>22.08</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
         <v>55289</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>111156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46184</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>29.97</v>
@@ -683,25 +730,31 @@
       <c r="J5">
         <v>20.68</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
         <v>81560</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>115626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46188</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>39</v>
@@ -718,13 +771,19 @@
       <c r="J6">
         <v>60.84</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6">
         <v>279830</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M6">
+        <v>113357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -732,18 +791,18 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>7</v>
@@ -752,9 +811,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="7">
         <v>121</v>
@@ -772,9 +831,9 @@
         <v>189.16</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>61.97</v>
@@ -792,9 +851,9 @@
         <v>42.76</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13" s="10">
         <v>182.97</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -49,16 +49,10 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
-    <t>Варна Евkсиноград</t>
+    <t>В8981ВР</t>
   </si>
   <si>
     <t>В5782КН</t>
@@ -67,7 +61,7 @@
     <t>В7241ВР</t>
   </si>
   <si>
-    <t>В8981ВР</t>
+    <t>78970155027721392</t>
   </si>
   <si>
     <t>78970155027721376</t>
@@ -76,28 +70,28 @@
     <t>78970155027721400</t>
   </si>
   <si>
-    <t>78970155027721392</t>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>16:14</t>
-  </si>
-  <si>
-    <t>12:13</t>
+    <t>2026-06-17 14:25:34</t>
+  </si>
+  <si>
+    <t>2026-06-22 09:14:03</t>
+  </si>
+  <si>
+    <t>2026-06-24 13:49:39</t>
+  </si>
+  <si>
+    <t>2026-06-24 13:53:22</t>
+  </si>
+  <si>
+    <t>2026-06-24 15:30:59</t>
+  </si>
+  <si>
+    <t>2026-06-24 15:33:39</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -517,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,12 +524,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,309 +561,308 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46177</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>30.48</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H2">
+        <v>20.12</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J2">
+        <v>20.42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>39</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>57.72</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>58.89</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>61.6</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>62.8</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="F4">
+        <v>27.46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>17.85</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>18.12</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H5">
+        <v>14.8</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J5">
+        <v>15.1</v>
+      </c>
+      <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="L2">
-        <v>279360</v>
-      </c>
-      <c r="M2">
-        <v>107346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H6">
+        <v>17.76</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J6">
+        <v>18.12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>42</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H3">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J3">
-        <v>65.52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>279530</v>
-      </c>
-      <c r="M3">
-        <v>109665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F7">
+        <v>35.73</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H7">
+        <v>23.22</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J7">
+        <v>23.58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7">
+        <v>93.67</v>
+      </c>
+      <c r="C12" s="7">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.6533</v>
+      </c>
+      <c r="E12" s="7">
+        <v>61.19</v>
+      </c>
+      <c r="F12" s="7">
+        <v>62.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>32</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H4">
-        <v>21.76</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J4">
-        <v>22.08</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>55289</v>
-      </c>
-      <c r="M4">
-        <v>111156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>29.97</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H5">
-        <v>20.38</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J5">
-        <v>20.68</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>81560</v>
-      </c>
-      <c r="M5">
-        <v>115626</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46188</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H6">
-        <v>59.67</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J6">
-        <v>60.84</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6">
-        <v>279830</v>
-      </c>
-      <c r="M6">
-        <v>113357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B13" s="7">
+        <v>61</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="E13" s="7">
+        <v>90.28</v>
+      </c>
+      <c r="F13" s="7">
+        <v>92.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="7">
-        <v>121</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.5333</v>
-      </c>
-      <c r="E11" s="7">
-        <v>185.53</v>
-      </c>
-      <c r="F11" s="7">
-        <v>189.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7">
-        <v>61.97</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="E12" s="7">
-        <v>42.14</v>
-      </c>
-      <c r="F12" s="7">
-        <v>42.76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="10">
-        <v>182.97</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>227.67</v>
-      </c>
-      <c r="F13" s="10">
-        <v>231.92</v>
+      <c r="B14" s="10">
+        <v>154.67</v>
+      </c>
+      <c r="C14" s="10">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10">
+        <v>151.47</v>
+      </c>
+      <c r="F14" s="10">
+        <v>154.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>В8981ВР</t>
@@ -76,22 +85,49 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-17 14:25:34</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:14:03</t>
-  </si>
-  <si>
-    <t>2026-06-24 13:49:39</t>
-  </si>
-  <si>
-    <t>2026-06-24 13:53:22</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:30:59</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:33:39</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
+  </si>
+  <si>
+    <t>09:13:00</t>
+  </si>
+  <si>
+    <t>13:49:00</t>
+  </si>
+  <si>
+    <t>13:53:00</t>
+  </si>
+  <si>
+    <t>15:33:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>10:48:00</t>
+  </si>
+  <si>
+    <t>3233481380 3233481380</t>
+  </si>
+  <si>
+    <t>3233718742 3233718742</t>
+  </si>
+  <si>
+    <t>3233811670 3233811670</t>
+  </si>
+  <si>
+    <t>3233812739 3233812739</t>
+  </si>
+  <si>
+    <t>3233815626 3233815626</t>
+  </si>
+  <si>
+    <t>3233815818 3233815818</t>
+  </si>
+  <si>
+    <t>3234104016 3234104016</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -511,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,14 +556,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,308 +600,415 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46190</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>30.48</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
         <v>0.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>20.12</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.67</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>20.42</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>81820</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46195</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>39</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
         <v>1.48</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>57.72</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>58.89</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>280142</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46197</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>27.46</v>
-      </c>
-      <c r="G4" s="1">
+        <v>27.45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
-        <v>17.85</v>
-      </c>
       <c r="I4" s="1">
+        <v>17.84</v>
+      </c>
+      <c r="J4">
         <v>0.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>18.12</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>82000</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>14.8</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>15.1</v>
       </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>82000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46197</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.48</v>
+        <v>35.73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>17.76</v>
+        <v>0.65</v>
       </c>
       <c r="I6" s="1">
-        <v>1.51</v>
+        <v>23.22</v>
       </c>
       <c r="J6">
-        <v>18.12</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K6" s="1">
+        <v>23.58</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46197</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>1.48</v>
+      </c>
+      <c r="I7" s="1">
+        <v>17.76</v>
+      </c>
+      <c r="J7">
+        <v>1.51</v>
+      </c>
+      <c r="K7" s="1">
+        <v>18.12</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7">
+        <v>55540</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>35.73</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8">
+        <v>30.54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8">
         <v>0.65</v>
       </c>
-      <c r="H7">
-        <v>23.22</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="I8" s="1">
+        <v>19.85</v>
+      </c>
+      <c r="J8">
         <v>0.66</v>
       </c>
-      <c r="J7">
-        <v>23.58</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="K8" s="1">
+        <v>20.16</v>
+      </c>
+      <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="M8">
+        <v>82251</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="7">
+        <v>124.2</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.6524</v>
+      </c>
+      <c r="E13" s="7">
+        <v>81.03</v>
+      </c>
+      <c r="F13" s="7">
+        <v>82.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7">
+        <v>61</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="E14" s="7">
+        <v>90.28</v>
+      </c>
+      <c r="F14" s="7">
+        <v>92.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="10">
+        <v>185.2</v>
+      </c>
+      <c r="C15" s="10">
         <v>7</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7">
-        <v>93.67</v>
-      </c>
-      <c r="C12" s="7">
-        <v>3</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.6533</v>
-      </c>
-      <c r="E12" s="7">
-        <v>61.19</v>
-      </c>
-      <c r="F12" s="7">
-        <v>62.12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="7">
-        <v>61</v>
-      </c>
-      <c r="C13" s="7">
-        <v>3</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.48</v>
-      </c>
-      <c r="E13" s="7">
-        <v>90.28</v>
-      </c>
-      <c r="F13" s="7">
-        <v>92.11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="10">
-        <v>154.67</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>151.47</v>
-      </c>
-      <c r="F14" s="10">
-        <v>154.23</v>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>171.31</v>
+      </c>
+      <c r="F15" s="10">
+        <v>174.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В8981ВР</t>
@@ -85,49 +82,25 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:25:00</t>
-  </si>
-  <si>
-    <t>09:13:00</t>
-  </si>
-  <si>
-    <t>13:49:00</t>
-  </si>
-  <si>
-    <t>13:53:00</t>
-  </si>
-  <si>
-    <t>15:33:00</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>10:48:00</t>
-  </si>
-  <si>
-    <t>3233481380 3233481380</t>
-  </si>
-  <si>
-    <t>3233718742 3233718742</t>
-  </si>
-  <si>
-    <t>3233811670 3233811670</t>
-  </si>
-  <si>
-    <t>3233812739 3233812739</t>
-  </si>
-  <si>
-    <t>3233815626 3233815626</t>
-  </si>
-  <si>
-    <t>3233815818 3233815818</t>
-  </si>
-  <si>
-    <t>3234104016 3234104016</t>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>10:49</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -547,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -556,17 +529,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,321 +578,297 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46190</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>30.48</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
+      <c r="G2" s="1">
+        <v>0.66</v>
       </c>
       <c r="H2">
-        <v>0.66</v>
+        <v>20.12</v>
       </c>
       <c r="I2" s="1">
-        <v>20.12</v>
+        <v>0.67</v>
       </c>
       <c r="J2">
-        <v>0.67</v>
-      </c>
-      <c r="K2" s="1">
         <v>20.42</v>
       </c>
-      <c r="L2" t="s">
-        <v>24</v>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>81820</v>
       </c>
       <c r="M2">
-        <v>81820</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>114433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46195</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>39</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>57.72</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>58.89</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="H3">
-        <v>1.48</v>
-      </c>
-      <c r="I3" s="1">
-        <v>57.72</v>
-      </c>
-      <c r="J3">
-        <v>1.51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>58.89</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
+      <c r="L3">
+        <v>280142</v>
       </c>
       <c r="M3">
-        <v>280142</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>116902</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46197</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>27.45</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
+        <v>27.46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>0.65</v>
+        <v>17.85</v>
       </c>
       <c r="I4" s="1">
-        <v>17.84</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
         <v>18.12</v>
       </c>
-      <c r="L4" t="s">
-        <v>26</v>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>82000</v>
       </c>
       <c r="M4">
-        <v>82000</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>118215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
-        <v>23</v>
+      <c r="G5" s="1">
+        <v>1.48</v>
       </c>
       <c r="H5">
-        <v>1.48</v>
+        <v>14.8</v>
       </c>
       <c r="I5" s="1">
-        <v>14.8</v>
+        <v>1.51</v>
       </c>
       <c r="J5">
-        <v>1.51</v>
-      </c>
-      <c r="K5" s="1">
         <v>15.1</v>
       </c>
-      <c r="L5" t="s">
-        <v>27</v>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>82000</v>
       </c>
       <c r="M5">
-        <v>82000</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46197</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
       <c r="F6">
-        <v>35.73</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.48</v>
       </c>
       <c r="H6">
-        <v>0.65</v>
+        <v>17.76</v>
       </c>
       <c r="I6" s="1">
-        <v>23.22</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
-        <v>23.58</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
+        <v>18.12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>55540</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>118290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46197</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
       <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
+        <v>35.73</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
       </c>
       <c r="H7">
-        <v>1.48</v>
+        <v>23.22</v>
       </c>
       <c r="I7" s="1">
-        <v>17.76</v>
+        <v>0.66</v>
       </c>
       <c r="J7">
-        <v>1.51</v>
-      </c>
-      <c r="K7" s="1">
-        <v>18.12</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
+        <v>23.58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>55540</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>118295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46203</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>30.54</v>
       </c>
-      <c r="G8" t="s">
-        <v>23</v>
+      <c r="G8" s="1">
+        <v>0.65</v>
       </c>
       <c r="H8">
-        <v>0.65</v>
+        <v>19.85</v>
       </c>
       <c r="I8" s="1">
-        <v>19.85</v>
+        <v>0.66</v>
       </c>
       <c r="J8">
-        <v>0.66</v>
-      </c>
-      <c r="K8" s="1">
         <v>20.16</v>
       </c>
-      <c r="L8" t="s">
-        <v>30</v>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>82251</v>
       </c>
       <c r="M8">
-        <v>82251</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>121508</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -928,32 +876,32 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="7">
-        <v>124.2</v>
+        <v>124.21</v>
       </c>
       <c r="C13" s="7">
         <v>4</v>
@@ -962,15 +910,15 @@
         <v>0.6524</v>
       </c>
       <c r="E13" s="7">
-        <v>81.03</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F13" s="7">
         <v>82.28</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="7">
         <v>61</v>
@@ -988,19 +936,19 @@
         <v>92.11</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B15" s="10">
-        <v>185.2</v>
+        <v>185.21</v>
       </c>
       <c r="C15" s="10">
         <v>7</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="10">
-        <v>171.31</v>
+        <v>171.32</v>
       </c>
       <c r="F15" s="10">
         <v>174.39</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,37 +55,46 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>В7241ВР</t>
   </si>
   <si>
     <t>В8981ВР</t>
   </si>
   <si>
-    <t>В6514КС</t>
+    <t>78970155027721400</t>
   </si>
   <si>
     <t>78970155027721392</t>
   </si>
   <si>
-    <t>78970155027721384</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>2026-07-07 14:52:50</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:42:25</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:03:13</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>3235092263 3235092263</t>
+  </si>
+  <si>
+    <t>3235187472 3235187472</t>
+  </si>
+  <si>
+    <t>3235586860 3235586860</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -502,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,15 +523,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -556,124 +570,148 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>37.25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>23.47</v>
+      </c>
+      <c r="J2">
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>23.84</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>55831</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>31.36</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H2">
-        <v>19.44</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>32.22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
         <v>0.63</v>
       </c>
-      <c r="J2">
-        <v>19.76</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>82512</v>
+      <c r="I3" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>20.62</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
+        <v>83000</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="F3">
-        <v>26.56</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H3">
-        <v>16.47</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J3">
-        <v>16.73</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>82235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4">
-        <v>47</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.46</v>
+        <v>27.02</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>68.62</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>1.49</v>
+        <v>17.02</v>
       </c>
       <c r="J4">
-        <v>70.03</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>261224</v>
+        <v>0.64</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17.29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>83363</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -681,82 +719,62 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
-        <v>57.92</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="C9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="8">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="E9" s="7">
-        <v>35.91</v>
+        <v>60.79</v>
       </c>
       <c r="F9" s="7">
-        <v>36.49</v>
+        <v>61.75</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>47</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.46</v>
-      </c>
-      <c r="E10" s="7">
-        <v>68.62</v>
-      </c>
-      <c r="F10" s="7">
-        <v>70.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="10">
-        <v>104.92</v>
-      </c>
-      <c r="C11" s="10">
+    <row r="10" spans="1:14">
+      <c r="A10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="10">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="C10" s="10">
         <v>3</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>104.53</v>
-      </c>
-      <c r="F11" s="10">
-        <v>106.52</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>60.79</v>
+      </c>
+      <c r="F10" s="10">
+        <v>61.75</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -122,7 +122,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -750,7 +750,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="8">
-        <v>0.63</v>
+        <v>0.630013</v>
       </c>
       <c r="E9" s="7">
         <v>60.79</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -527,13 +530,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,142 +579,154 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46223</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>37.25</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.63</v>
       </c>
-      <c r="I2" s="1">
-        <v>23.47</v>
-      </c>
       <c r="J2">
+        <v>23.4675</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.64</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>23.84</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
         <v>55831</v>
       </c>
-      <c r="N2" t="s">
-        <v>24</v>
+      <c r="O2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>32.22</v>
+        <v>32.219</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>20.3</v>
-      </c>
       <c r="J3">
+        <v>20.29797</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>20.62</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>20.62016</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>83000</v>
       </c>
-      <c r="N3" t="s">
-        <v>25</v>
+      <c r="O3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46233</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>27.02</v>
+        <v>27.016</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>17.02</v>
-      </c>
       <c r="J4">
+        <v>17.02008</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>17.29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>17.29024</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4">
         <v>83363</v>
       </c>
-      <c r="N4" t="s">
-        <v>26</v>
+      <c r="O4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -719,38 +734,38 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
-        <v>96.48999999999999</v>
+        <v>96.485</v>
       </c>
       <c r="C9" s="7">
         <v>3</v>
       </c>
       <c r="D9" s="8">
-        <v>0.630013</v>
+        <v>0.63</v>
       </c>
       <c r="E9" s="7">
         <v>60.79</v>
@@ -759,12 +774,12 @@
         <v>61.75</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="10">
-        <v>96.48999999999999</v>
+        <v>96.485</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -123,9 +120,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -219,10 +216,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,13 +527,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,154 +576,142 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46223</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>37.25</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>23.468</v>
+      </c>
+      <c r="J2">
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>23.84</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J2">
-        <v>23.4675</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L2" s="1">
-        <v>23.84</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>55831</v>
       </c>
-      <c r="O2" t="s">
-        <v>25</v>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>32.219</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>20.298</v>
       </c>
       <c r="J3">
-        <v>20.29797</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>20.62016</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+        <v>20.62</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>83000</v>
       </c>
-      <c r="O3" t="s">
-        <v>26</v>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46233</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
       </c>
       <c r="F4">
         <v>27.016</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>17.02</v>
       </c>
       <c r="J4">
-        <v>17.02008</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>17.29024</v>
-      </c>
-      <c r="M4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4">
+        <v>17.29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
         <v>83363</v>
       </c>
-      <c r="O4" t="s">
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -734,49 +719,49 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>96.485</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>3</v>
       </c>
       <c r="D9" s="8">
         <v>0.63</v>
       </c>
-      <c r="E9" s="7">
-        <v>60.79</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="8">
+        <v>60.786</v>
+      </c>
+      <c r="F9" s="8">
         <v>61.75</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="10">
         <v>96.485</v>
@@ -786,7 +771,7 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10">
-        <v>60.79</v>
+        <v>60.786</v>
       </c>
       <c r="F10" s="10">
         <v>61.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,43 +55,40 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>В7241ВР</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В8981ВР</t>
   </si>
   <si>
-    <t>78970155027721400</t>
+    <t>В6514КС</t>
   </si>
   <si>
     <t>78970155027721392</t>
   </si>
   <si>
+    <t>78970155027721384</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:40:00</t>
-  </si>
-  <si>
-    <t>10:38:00</t>
-  </si>
-  <si>
-    <t>14:15:00</t>
-  </si>
-  <si>
-    <t>3235092263 3235092263</t>
-  </si>
-  <si>
-    <t>3235187472 3235187472</t>
-  </si>
-  <si>
-    <t>3235586860 3235586860</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>15:32</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>09:43</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -120,9 +114,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -216,10 +210,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -523,17 +517,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,16 +566,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46223</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -594,83 +584,77 @@
         <v>19</v>
       </c>
       <c r="F2">
-        <v>37.25</v>
-      </c>
-      <c r="G2" t="s">
+        <v>30.303</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>19.697</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>0.63</v>
-      </c>
-      <c r="I2" s="1">
-        <v>23.468</v>
-      </c>
-      <c r="J2">
-        <v>0.64</v>
-      </c>
-      <c r="K2" s="1">
-        <v>23.84</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
+      <c r="L2">
+        <v>83626</v>
+      </c>
       <c r="M2">
-        <v>55831</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>141147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46225</v>
+        <v>46241</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>32.219</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>31.152</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.63</v>
+        <v>20.249</v>
       </c>
       <c r="I3" s="1">
-        <v>20.298</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>20.62</v>
-      </c>
-      <c r="L3" t="s">
+        <v>20.56</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
+      <c r="L3">
+        <v>83871</v>
+      </c>
       <c r="M3">
-        <v>83000</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>142945</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -679,107 +663,165 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>69.92</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J4">
+        <v>71.3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
+        <v>261685</v>
+      </c>
+      <c r="M4">
+        <v>145535</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F4">
-        <v>27.016</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F5">
+        <v>31.409</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>20.416</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>20.73</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>84132</v>
+      </c>
+      <c r="M5">
+        <v>140380</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>92.864</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>60.36</v>
+      </c>
+      <c r="F10" s="7">
+        <v>61.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H4">
-        <v>0.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.02</v>
-      </c>
-      <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
-        <v>83363</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B11" s="7">
+        <v>46</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E11" s="7">
+        <v>69.92</v>
+      </c>
+      <c r="F11" s="7">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>96.485</v>
-      </c>
-      <c r="C9" s="8">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E9" s="8">
-        <v>60.786</v>
-      </c>
-      <c r="F9" s="8">
-        <v>61.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="10">
-        <v>96.485</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>60.786</v>
-      </c>
-      <c r="F10" s="10">
-        <v>61.75</v>
+      <c r="B12" s="10">
+        <v>138.864</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>130.28</v>
+      </c>
+      <c r="F12" s="10">
+        <v>132.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,40 +58,43 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>В8981ВР</t>
   </si>
   <si>
-    <t>В6514КС</t>
+    <t>В7241ВР</t>
   </si>
   <si>
     <t>78970155027721392</t>
   </si>
   <si>
-    <t>78970155027721384</t>
+    <t>78970155027721400</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>15:32</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>10:08</t>
-  </si>
-  <si>
-    <t>09:43</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:52:00</t>
+  </si>
+  <si>
+    <t>15:47:00</t>
+  </si>
+  <si>
+    <t>14:48:00</t>
+  </si>
+  <si>
+    <t>3236618293 3236618293</t>
+  </si>
+  <si>
+    <t>3236716697 3236716697</t>
+  </si>
+  <si>
+    <t>3237014230 3237014230</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
@@ -113,10 +119,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -196,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -210,10 +217,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,16 +526,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -566,13 +576,16 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -584,244 +597,192 @@
         <v>19</v>
       </c>
       <c r="F2">
-        <v>30.303</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2">
-        <v>19.697</v>
+        <v>31.79</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
       </c>
       <c r="I2" s="1">
+        <v>31.472</v>
+      </c>
+      <c r="J2" s="1">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1">
+        <v>20.981</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>83626</v>
-      </c>
       <c r="M2">
-        <v>141147</v>
+        <v>84421</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>31.152</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>20.249</v>
+        <v>35.92</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
       </c>
       <c r="I3" s="1">
+        <v>35.561</v>
+      </c>
+      <c r="J3" s="1">
         <v>0.66</v>
       </c>
-      <c r="J3">
-        <v>20.56</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1">
+        <v>23.707</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>83871</v>
-      </c>
       <c r="M3">
-        <v>142945</v>
+        <v>56105</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46245</v>
+        <v>46261</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>30.62</v>
+      </c>
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>69.92</v>
+      <c r="H4" s="1">
+        <v>0.99</v>
       </c>
       <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>71.3</v>
-      </c>
-      <c r="K4" t="s">
+        <v>30.314</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="1">
+        <v>20.209</v>
+      </c>
+      <c r="L4" t="s">
         <v>23</v>
       </c>
-      <c r="L4">
-        <v>261685</v>
-      </c>
       <c r="M4">
-        <v>145535</v>
+        <v>84701</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F5">
-        <v>31.409</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5">
-        <v>20.416</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J5">
-        <v>20.73</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>84132</v>
-      </c>
-      <c r="M5">
-        <v>140380</v>
+      <c r="B9" s="7">
+        <v>98.33</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E9" s="7">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="F9" s="7">
+        <v>64.90000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>92.864</v>
-      </c>
-      <c r="C10" s="7">
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="11">
+        <v>98.33</v>
+      </c>
+      <c r="C10" s="12">
         <v>3</v>
       </c>
-      <c r="D10" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>60.36</v>
-      </c>
-      <c r="F10" s="7">
-        <v>61.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="7">
-        <v>46</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E11" s="7">
-        <v>69.92</v>
-      </c>
-      <c r="F11" s="7">
-        <v>71.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="10">
-        <v>138.864</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>130.28</v>
-      </c>
-      <c r="F12" s="10">
-        <v>132.59</v>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="F10" s="11">
+        <v>64.90000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА/РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА.xlsx
@@ -603,10 +603,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>31.472</v>
+        <v>20.664</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -647,10 +647,10 @@
         <v>20</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>35.561</v>
+        <v>23.348</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -691,10 +691,10 @@
         <v>20</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>30.314</v>
+        <v>19.903</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -753,10 +753,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="9">
-        <v>0.99</v>
+        <v>0.65001</v>
       </c>
       <c r="E9" s="7">
-        <v>97.34999999999999</v>
+        <v>63.92</v>
       </c>
       <c r="F9" s="7">
         <v>64.90000000000001</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11">
-        <v>97.34999999999999</v>
+        <v>63.92</v>
       </c>
       <c r="F10" s="11">
         <v>64.90000000000001</v>
